--- a/SGC-CKN/Excel/056628cc-e93d-4e67-922a-521eac97817e_P1-156_P1-136_D800_27-03-2026.xlsx
+++ b/SGC-CKN/Excel/056628cc-e93d-4e67-922a-521eac97817e_P1-156_P1-136_D800_27-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
   <si>
     <t>Dự án</t>
   </si>
@@ -106,7 +106,7 @@
 27/03/2026</t>
   </si>
   <si>
-    <t>Đoạn đầu từ đỉnh casing (0.56) đến 1.5m</t>
+    <t/>
   </si>
   <si>
     <t>3</t>
@@ -117,9 +117,6 @@
   <si>
     <t xml:space="preserve">02:40
 27/03/2026</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>5</t>
@@ -348,12 +345,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFDDD6FE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDD6FE"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -517,17 +514,17 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1198,24 +1195,24 @@
         <v>6.2</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13" s="12">
         <v>-4.6</v>
@@ -1233,94 +1230,94 @@
         <v>5.83</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="17" t="s">
         <v>39</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="15">
         <v>-8</v>
       </c>
       <c r="G14" s="15">
-        <v>-14.5</v>
+        <v>-16.5</v>
       </c>
       <c r="H14" s="15">
         <v>1.5</v>
       </c>
       <c r="I14" s="15">
-        <v>6.5</v>
-      </c>
-      <c r="J14" s="18">
-        <v>4.33</v>
+        <v>8.5</v>
+      </c>
+      <c r="J14" s="8">
+        <v>5.67</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="20" t="s">
+      <c r="D15" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="19">
-        <v>-14.5</v>
-      </c>
-      <c r="G15" s="19">
+      <c r="F15" s="18">
+        <v>-16.5</v>
+      </c>
+      <c r="G15" s="18">
         <v>-22</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="18">
         <v>1.25</v>
       </c>
-      <c r="I15" s="19">
-        <v>7.5</v>
-      </c>
-      <c r="J15" s="8">
-        <v>6</v>
-      </c>
-      <c r="K15" s="20" t="s">
-        <v>34</v>
+      <c r="I15" s="18">
+        <v>5.5</v>
+      </c>
+      <c r="J15" s="21">
+        <v>4.4</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="24" t="s">
         <v>45</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>46</v>
       </c>
       <c r="F16" s="22">
         <v>-22</v>
@@ -1338,24 +1335,24 @@
         <v>10.68</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="27" t="s">
         <v>48</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>49</v>
       </c>
       <c r="F17" s="25">
         <v>-25.56</v>
@@ -1373,24 +1370,24 @@
         <v>5.04</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>51</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>52</v>
       </c>
       <c r="F18" s="28">
         <v>-39.6</v>
@@ -1404,16 +1401,16 @@
       <c r="I18" s="28">
         <v>4.41</v>
       </c>
-      <c r="J18" s="18">
+      <c r="J18" s="21">
         <v>2.07</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1519,31 +1516,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1612,7 +1609,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1641,7 +1638,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1650,45 +1647,45 @@
         <v>-8</v>
       </c>
       <c r="F5" s="15">
-        <v>-14.5</v>
+        <v>-16.5</v>
       </c>
       <c r="G5" s="15">
         <v>1.5</v>
       </c>
       <c r="H5" s="15">
-        <v>6.5</v>
-      </c>
-      <c r="I5" s="18">
-        <v>4.33</v>
+        <v>8.5</v>
+      </c>
+      <c r="I5" s="8">
+        <v>5.67</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="19">
+      <c r="C6" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="18">
         <v>1</v>
       </c>
-      <c r="E6" s="19">
-        <v>-14.5</v>
-      </c>
-      <c r="F6" s="19">
+      <c r="E6" s="18">
+        <v>-16.5</v>
+      </c>
+      <c r="F6" s="18">
         <v>-22</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="18">
         <v>1.25</v>
       </c>
-      <c r="H6" s="19">
-        <v>7.5</v>
-      </c>
-      <c r="I6" s="8">
-        <v>6</v>
+      <c r="H6" s="18">
+        <v>5.5</v>
+      </c>
+      <c r="I6" s="21">
+        <v>4.4</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1699,7 +1696,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1728,7 +1725,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1757,7 +1754,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1774,19 +1771,19 @@
       <c r="H9" s="28">
         <v>4.41</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="21">
         <v>2.07</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D10" s="33">
         <v>8</v>

--- a/SGC-CKN/Excel/056628cc-e93d-4e67-922a-521eac97817e_P1-156_P1-136_D800_27-03-2026.xlsx
+++ b/SGC-CKN/Excel/056628cc-e93d-4e67-922a-521eac97817e_P1-156_P1-136_D800_27-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
   <si>
     <t>Dự án</t>
   </si>
@@ -106,7 +106,7 @@
 27/03/2026</t>
   </si>
   <si>
-    <t/>
+    <t>Đoạn đầu từ đỉnh casing (0.56) đến 1.5m</t>
   </si>
   <si>
     <t>3</t>
@@ -117,6 +117,9 @@
   <si>
     <t xml:space="preserve">02:40
 27/03/2026</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>5</t>
@@ -345,12 +348,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDD6FE"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFDDD6FE"/>
       </patternFill>
     </fill>
     <fill>
@@ -514,17 +517,17 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1195,24 +1198,24 @@
         <v>6.2</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F13" s="12">
         <v>-4.6</v>
@@ -1230,94 +1233,94 @@
         <v>5.83</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="15">
         <v>-8</v>
       </c>
       <c r="G14" s="15">
-        <v>-16.5</v>
+        <v>-14.5</v>
       </c>
       <c r="H14" s="15">
         <v>1.5</v>
       </c>
       <c r="I14" s="15">
-        <v>8.5</v>
-      </c>
-      <c r="J14" s="8">
-        <v>5.67</v>
+        <v>6.5</v>
+      </c>
+      <c r="J14" s="18">
+        <v>4.33</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="18">
-        <v>-16.5</v>
-      </c>
-      <c r="G15" s="18">
+      <c r="E15" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="19">
+        <v>-14.5</v>
+      </c>
+      <c r="G15" s="19">
         <v>-22</v>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="19">
         <v>1.25</v>
       </c>
-      <c r="I15" s="18">
-        <v>5.5</v>
-      </c>
-      <c r="J15" s="21">
-        <v>4.4</v>
-      </c>
-      <c r="K15" s="19" t="s">
-        <v>30</v>
+      <c r="I15" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="J15" s="8">
+        <v>6</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" s="22">
         <v>-22</v>
@@ -1335,24 +1338,24 @@
         <v>10.68</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F17" s="25">
         <v>-25.56</v>
@@ -1370,24 +1373,24 @@
         <v>5.04</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" s="28">
         <v>-39.6</v>
@@ -1401,16 +1404,16 @@
       <c r="I18" s="28">
         <v>4.41</v>
       </c>
-      <c r="J18" s="21">
+      <c r="J18" s="18">
         <v>2.07</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1516,31 +1519,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1609,7 +1612,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1638,7 +1641,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1647,45 +1650,45 @@
         <v>-8</v>
       </c>
       <c r="F5" s="15">
-        <v>-16.5</v>
+        <v>-14.5</v>
       </c>
       <c r="G5" s="15">
         <v>1.5</v>
       </c>
       <c r="H5" s="15">
-        <v>8.5</v>
-      </c>
-      <c r="I5" s="8">
-        <v>5.67</v>
+        <v>6.5</v>
+      </c>
+      <c r="I5" s="18">
+        <v>4.33</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="18">
+      <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="18">
+      <c r="C6" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="19">
         <v>1</v>
       </c>
-      <c r="E6" s="18">
-        <v>-16.5</v>
-      </c>
-      <c r="F6" s="18">
+      <c r="E6" s="19">
+        <v>-14.5</v>
+      </c>
+      <c r="F6" s="19">
         <v>-22</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="19">
         <v>1.25</v>
       </c>
-      <c r="H6" s="18">
-        <v>5.5</v>
-      </c>
-      <c r="I6" s="21">
-        <v>4.4</v>
+      <c r="H6" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="I6" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1696,7 +1699,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1725,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1754,7 +1757,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1771,19 +1774,19 @@
       <c r="H9" s="28">
         <v>4.41</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="18">
         <v>2.07</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D10" s="33">
         <v>8</v>
